--- a/AAII_Financials/Quarterly/CIBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CIBN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>CIBN</t>
   </si>
@@ -656,153 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43008</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42825</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42643</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3500</v>
       </c>
       <c r="F8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H8" s="3">
         <v>2600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1500</v>
       </c>
       <c r="R8" s="3">
         <v>1500</v>
@@ -822,8 +824,11 @@
       <c r="W8" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -887,8 +892,11 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -952,8 +960,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -977,8 +988,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1042,8 +1054,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1107,8 +1122,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1172,8 +1190,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1237,8 +1258,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1259,61 +1283,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1500</v>
       </c>
       <c r="F17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
       </c>
       <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>2500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
-      </c>
-      <c r="T17" s="3">
-        <v>300</v>
       </c>
       <c r="U17" s="3">
         <v>300</v>
@@ -1322,63 +1347,66 @@
         <v>300</v>
       </c>
       <c r="W17" s="3">
+        <v>300</v>
+      </c>
+      <c r="X17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2000</v>
       </c>
       <c r="F18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H18" s="3">
         <v>1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>7400</v>
       </c>
-      <c r="I18" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1200</v>
       </c>
       <c r="U18" s="3">
         <v>1200</v>
@@ -1387,10 +1415,13 @@
         <v>1200</v>
       </c>
       <c r="W18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X18" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1414,73 +1445,77 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1600</v>
       </c>
       <c r="F20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="Q20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="T20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1544,8 +1579,11 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1609,8 +1647,11 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1618,64 +1659,67 @@
         <v>400</v>
       </c>
       <c r="E23" s="3">
+        <v>400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
       </c>
-      <c r="J23" s="3">
-        <v>500</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1683,50 +1727,50 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>400</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>400</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1734,13 +1778,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1804,138 +1851,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>300</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>200</v>
+      </c>
+      <c r="H26" s="3">
         <v>300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
-        <v>400</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
         <v>100</v>
       </c>
       <c r="V26" s="3">
+        <v>100</v>
+      </c>
+      <c r="W26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>300</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>200</v>
+      </c>
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
-        <v>400</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
         <v>100</v>
       </c>
       <c r="V27" s="3">
+        <v>100</v>
+      </c>
+      <c r="W27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1999,8 +2055,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2031,8 +2090,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
@@ -2046,11 +2105,11 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2064,8 +2123,11 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2129,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2194,138 +2259,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1600</v>
       </c>
       <c r="F32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="Q32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S32" s="3">
+        <v>800</v>
+      </c>
+      <c r="T32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4300</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>800</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="T32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
-        <v>900</v>
-      </c>
-      <c r="W32" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>300</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>200</v>
+      </c>
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
-        <v>400</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3">
         <v>100</v>
       </c>
       <c r="V33" s="3">
+        <v>100</v>
+      </c>
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2389,143 +2463,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>300</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>200</v>
+      </c>
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
-        <v>400</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
         <v>100</v>
       </c>
       <c r="V35" s="3">
+        <v>100</v>
+      </c>
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43008</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42825</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42643</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2549,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2574,93 +2658,97 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E41" s="3">
         <v>9200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
-        <v>29300</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3">
         <v>9400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E42" s="3">
         <v>4500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G42" s="3">
         <v>4200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I42" s="3">
-        <v>3700</v>
       </c>
       <c r="J42" s="3">
         <v>3500</v>
@@ -2669,10 +2757,10 @@
         <v>3500</v>
       </c>
       <c r="L42" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M42" s="3">
         <v>3400</v>
-      </c>
-      <c r="M42" s="3">
-        <v>3300</v>
       </c>
       <c r="N42" s="3">
         <v>3300</v>
@@ -2680,20 +2768,20 @@
       <c r="O42" s="3">
         <v>3300</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="P42" s="3">
         <v>3300</v>
       </c>
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="R42" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S42" s="3">
         <v>2500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2300</v>
-      </c>
-      <c r="T42" s="3">
-        <v>2200</v>
       </c>
       <c r="U42" s="3">
         <v>2200</v>
@@ -2704,8 +2792,11 @@
       <c r="W42" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2769,8 +2860,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2834,8 +2928,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2899,8 +2996,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2964,8 +3064,11 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3029,8 +3132,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3038,46 +3144,46 @@
         <v>5500</v>
       </c>
       <c r="E48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5800</v>
       </c>
-      <c r="I48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5400</v>
       </c>
       <c r="N48" s="3">
         <v>5400</v>
       </c>
       <c r="O48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>3800</v>
-      </c>
-      <c r="R48" s="3">
-        <v>3900</v>
       </c>
       <c r="S48" s="3">
         <v>3900</v>
@@ -3089,13 +3195,16 @@
         <v>3900</v>
       </c>
       <c r="V48" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="W48" s="3">
         <v>4000</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3106,7 +3215,7 @@
         <v>1400</v>
       </c>
       <c r="F49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G49" s="3">
         <v>1400</v>
@@ -3114,24 +3223,24 @@
       <c r="H49" s="3">
         <v>1400</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+      <c r="I49" s="3">
+        <v>1400</v>
       </c>
       <c r="J49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="L49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3144,23 +3253,26 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3224,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3289,8 +3404,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3354,8 +3472,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3419,73 +3540,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>295700</v>
+      </c>
+      <c r="E54" s="3">
         <v>288000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>271900</v>
+      </c>
+      <c r="G54" s="3">
         <v>261400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>253600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>244400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>233800</v>
       </c>
-      <c r="I54" s="3">
-        <v>234000</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>222400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>229700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>206800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>168900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>163200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>144100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3">
         <v>144100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>144200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>144700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>141900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>143200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>140300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3509,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3534,8 +3662,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3543,16 +3672,16 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>600</v>
+      </c>
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -3573,13 +3702,13 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3599,8 +3728,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3664,13 +3796,16 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -3678,59 +3813,62 @@
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I59" s="3">
-        <v>400</v>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3794,8 +3932,11 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3803,22 +3944,22 @@
         <v>4800</v>
       </c>
       <c r="E61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F61" s="3">
         <v>3400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>1000</v>
@@ -3827,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3859,34 +4000,37 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>200</v>
+      </c>
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
-        <v>700</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
@@ -3895,37 +4039,40 @@
         <v>400</v>
       </c>
       <c r="N62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="R62" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="S62" s="3">
         <v>600</v>
       </c>
       <c r="T62" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="U62" s="3">
         <v>500</v>
       </c>
       <c r="V62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W62" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3989,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4054,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4119,73 +4272,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>278500</v>
+      </c>
+      <c r="E66" s="3">
         <v>271800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
+        <v>255100</v>
+      </c>
+      <c r="G66" s="3">
         <v>244300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>236900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>228000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>217100</v>
       </c>
-      <c r="I66" s="3">
-        <v>215900</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>204800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>212500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>191100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>154700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>149400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>131100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R66" s="3">
         <v>131100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>131400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>130900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>132300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>129500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>130700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4209,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4274,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4339,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4404,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4469,73 +4638,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E72" s="3">
         <v>20800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>21200</v>
+      </c>
+      <c r="H72" s="3">
         <v>21100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>20900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>20800</v>
       </c>
-      <c r="I72" s="3">
-        <v>20300</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>15300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14500</v>
-      </c>
-      <c r="T72" s="3">
-        <v>14600</v>
       </c>
       <c r="U72" s="3">
         <v>14600</v>
       </c>
       <c r="V72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="W72" s="3">
         <v>14500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4599,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4664,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4729,73 +4910,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E76" s="3">
         <v>16300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>16800</v>
+      </c>
+      <c r="G76" s="3">
         <v>17100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>16600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16700</v>
       </c>
-      <c r="I76" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R76" s="3">
         <v>13000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12500</v>
-      </c>
-      <c r="T76" s="3">
-        <v>12400</v>
       </c>
       <c r="U76" s="3">
         <v>12400</v>
       </c>
       <c r="V76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W76" s="3">
         <v>12500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4859,143 +5046,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43008</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42825</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42643</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>300</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>200</v>
+      </c>
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
-        <v>400</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U81" s="3">
         <v>100</v>
       </c>
       <c r="V81" s="3">
+        <v>100</v>
+      </c>
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5019,8 +5215,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5084,8 +5281,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5149,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5214,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5279,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5344,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5409,8 +5621,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5474,8 +5689,11 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5499,8 +5717,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5564,8 +5783,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5629,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5694,8 +5919,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5759,8 +5987,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5784,8 +6015,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5849,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5914,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5979,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6044,8 +6285,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6109,8 +6353,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6174,8 +6421,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6237,6 +6487,9 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CIBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CIBN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>CIBN</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43008</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42825</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42643</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2600</v>
       </c>
       <c r="I8" s="3">
         <v>2600</v>
       </c>
       <c r="J8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K8" s="3">
         <v>8700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3400</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1500</v>
       </c>
       <c r="S8" s="3">
         <v>1500</v>
@@ -827,8 +831,11 @@
       <c r="X8" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -895,8 +902,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -963,8 +973,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1002,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1071,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,8 +1142,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1193,8 +1213,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1261,8 +1284,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,64 +1310,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
-      </c>
-      <c r="K17" s="3">
-        <v>400</v>
       </c>
       <c r="L17" s="3">
         <v>400</v>
       </c>
       <c r="M17" s="3">
+        <v>400</v>
+      </c>
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
-      </c>
-      <c r="U17" s="3">
-        <v>300</v>
       </c>
       <c r="V17" s="3">
         <v>300</v>
@@ -1350,10 +1377,13 @@
         <v>300</v>
       </c>
       <c r="X17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1364,52 +1394,52 @@
         <v>2000</v>
       </c>
       <c r="F18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>1200</v>
       </c>
       <c r="V18" s="3">
         <v>1200</v>
@@ -1418,10 +1448,13 @@
         <v>1200</v>
       </c>
       <c r="X18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,76 +1479,80 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="E20" s="3">
         <v>-1600</v>
       </c>
       <c r="F20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1500</v>
       </c>
       <c r="H20" s="3">
         <v>-1500</v>
       </c>
       <c r="I20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1582,8 +1619,11 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1650,130 +1690,136 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E23" s="3">
         <v>400</v>
       </c>
       <c r="F23" s="3">
+        <v>400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1781,13 +1827,16 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1903,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
         <v>300</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>300</v>
       </c>
       <c r="I26" s="3">
         <v>300</v>
       </c>
       <c r="J26" s="3">
+        <v>300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>300</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
         <v>100</v>
       </c>
       <c r="W26" s="3">
+        <v>100</v>
+      </c>
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
         <v>300</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>300</v>
       </c>
       <c r="I27" s="3">
         <v>300</v>
       </c>
       <c r="J27" s="3">
+        <v>300</v>
+      </c>
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>300</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>100</v>
       </c>
       <c r="W27" s="3">
+        <v>100</v>
+      </c>
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2116,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2093,8 +2154,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
@@ -2108,11 +2169,11 @@
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
@@ -2126,8 +2187,11 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2258,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,144 +2329,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E32" s="3">
         <v>1600</v>
       </c>
       <c r="F32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G32" s="3">
         <v>1800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1500</v>
       </c>
       <c r="H32" s="3">
         <v>1500</v>
       </c>
       <c r="I32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
         <v>300</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>300</v>
       </c>
       <c r="I33" s="3">
         <v>300</v>
       </c>
       <c r="J33" s="3">
+        <v>300</v>
+      </c>
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>300</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
         <v>100</v>
       </c>
       <c r="W33" s="3">
+        <v>100</v>
+      </c>
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2542,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
         <v>300</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>300</v>
       </c>
       <c r="I35" s="3">
         <v>300</v>
       </c>
       <c r="J35" s="3">
+        <v>300</v>
+      </c>
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>300</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>100</v>
       </c>
       <c r="W35" s="3">
+        <v>100</v>
+      </c>
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43008</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42825</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42643</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2718,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,99 +2745,103 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3">
         <v>9400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>4200</v>
       </c>
       <c r="H42" s="3">
         <v>4200</v>
       </c>
       <c r="I42" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J42" s="3">
         <v>3600</v>
-      </c>
-      <c r="J42" s="3">
-        <v>3500</v>
       </c>
       <c r="K42" s="3">
         <v>3500</v>
@@ -2760,10 +2850,10 @@
         <v>3500</v>
       </c>
       <c r="M42" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N42" s="3">
         <v>3400</v>
-      </c>
-      <c r="N42" s="3">
-        <v>3300</v>
       </c>
       <c r="O42" s="3">
         <v>3300</v>
@@ -2771,20 +2861,20 @@
       <c r="P42" s="3">
         <v>3300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="Q42" s="3">
         <v>3300</v>
       </c>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="S42" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T42" s="3">
         <v>2500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2300</v>
-      </c>
-      <c r="U42" s="3">
-        <v>2200</v>
       </c>
       <c r="V42" s="3">
         <v>2200</v>
@@ -2795,8 +2885,11 @@
       <c r="X42" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2863,8 +2956,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2931,8 +3027,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2999,8 +3098,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3067,8 +3169,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3135,58 +3240,61 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="E48" s="3">
         <v>5500</v>
       </c>
       <c r="F48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G48" s="3">
         <v>5600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>5700</v>
       </c>
       <c r="H48" s="3">
         <v>5700</v>
       </c>
       <c r="I48" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="J48" s="3">
         <v>5800</v>
       </c>
       <c r="K48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L48" s="3">
         <v>6100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5400</v>
       </c>
       <c r="O48" s="3">
         <v>5400</v>
       </c>
       <c r="P48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>3800</v>
-      </c>
-      <c r="S48" s="3">
-        <v>3900</v>
       </c>
       <c r="T48" s="3">
         <v>3900</v>
@@ -3198,13 +3306,16 @@
         <v>3900</v>
       </c>
       <c r="W48" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="X48" s="3">
         <v>4000</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3215,10 +3326,10 @@
         <v>1400</v>
       </c>
       <c r="F49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G49" s="3">
         <v>1300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1400</v>
       </c>
       <c r="H49" s="3">
         <v>1400</v>
@@ -3230,20 +3341,20 @@
         <v>1400</v>
       </c>
       <c r="K49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3">
         <v>900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3256,23 +3367,26 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3453,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,8 +3524,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3475,8 +3595,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3666,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E54" s="3">
         <v>295700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>288000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>271900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>261400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>253600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>233800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>222400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>229700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>206800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>168900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>163200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>144100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>144100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>144200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>143300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>144700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>141900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>143200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>140300</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3766,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,8 +3793,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3675,16 +3806,16 @@
         <v>700</v>
       </c>
       <c r="F57" s="3">
+        <v>700</v>
+      </c>
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
@@ -3705,13 +3836,13 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3731,8 +3862,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3799,25 +3933,28 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -3828,47 +3965,50 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3935,34 +4075,37 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4800</v>
+        <v>4400</v>
       </c>
       <c r="E61" s="3">
         <v>4800</v>
       </c>
       <c r="F61" s="3">
-        <v>3400</v>
+        <v>4800</v>
       </c>
       <c r="G61" s="3">
         <v>3400</v>
       </c>
       <c r="H61" s="3">
-        <v>1900</v>
+        <v>3400</v>
       </c>
       <c r="I61" s="3">
         <v>1900</v>
       </c>
       <c r="J61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K61" s="3">
         <v>900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1000</v>
       </c>
       <c r="L61" s="3">
         <v>1000</v>
@@ -3971,7 +4114,7 @@
         <v>1000</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -4003,8 +4146,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4012,28 +4158,28 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
       </c>
       <c r="G62" s="3">
+        <v>200</v>
+      </c>
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>400</v>
@@ -4042,37 +4188,40 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="S62" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="T62" s="3">
         <v>600</v>
       </c>
       <c r="U62" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V62" s="3">
         <v>500</v>
       </c>
       <c r="W62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X62" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4288,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4359,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,76 +4430,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E66" s="3">
         <v>278500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>271800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>255100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>244300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>236900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>228000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>217100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>204800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>212500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>191100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>154700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>149400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>131100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>131100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>131400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>130900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>132300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>129500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>130700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4530,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4599,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4670,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4741,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,76 +4812,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E72" s="3">
         <v>21100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>21200</v>
       </c>
       <c r="G72" s="3">
         <v>21200</v>
       </c>
       <c r="H72" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I72" s="3">
         <v>21100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>15300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14500</v>
-      </c>
-      <c r="U72" s="3">
-        <v>14600</v>
       </c>
       <c r="V72" s="3">
         <v>14600</v>
       </c>
       <c r="W72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="X72" s="3">
         <v>14500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4954,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5025,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5096,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E76" s="3">
         <v>17200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3">
         <v>13000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12500</v>
-      </c>
-      <c r="U76" s="3">
-        <v>12400</v>
       </c>
       <c r="V76" s="3">
         <v>12400</v>
       </c>
       <c r="W76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="X76" s="3">
         <v>12500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5238,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43008</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42825</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42643</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
         <v>300</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>300</v>
       </c>
       <c r="I81" s="3">
         <v>300</v>
       </c>
       <c r="J81" s="3">
+        <v>300</v>
+      </c>
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>300</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
         <v>100</v>
       </c>
       <c r="W81" s="3">
+        <v>100</v>
+      </c>
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5414,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5284,8 +5483,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5554,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5625,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5696,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5767,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,8 +5838,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5692,8 +5909,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,8 +5938,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5786,8 +6007,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6078,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,8 +6149,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5990,8 +6220,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6249,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6084,8 +6318,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6389,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6460,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,8 +6531,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6356,8 +6602,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6424,8 +6673,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6490,6 +6742,9 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>
